--- a/test-bills-sanitized.xlsx
+++ b/test-bills-sanitized.xlsx
@@ -48,7 +48,7 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Office Address: Unit No.1,GalaNo.2 &amp; 3,NearITI Circle,Road No.28,Kailash Nagar,Wagle Estate,Thane - 400 604,State- Maharashtra</t>
+          <t xml:space="preserve">Office Address: Unit No.1,GalaNo.2 &amp; 3,NearExample Circle,Road No.28,Example Nagar,Example Estate,Example City - 000 001,State- Maharashtra</t>
         </is>
       </c>
     </row>
@@ -124,7 +124,7 @@
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wagle Industrial Estate,</t>
+          <t xml:space="preserve">Example Industrial Estate,</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -149,7 +149,7 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thane - 400 604.</t>
+          <t xml:space="preserve">Example City - 000 001.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -206,7 +206,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">THANE                          </t>
+          <t xml:space="preserve">EXAMPLE CITY                   </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
